--- a/public/templates/AUTORIZACION_DE_DESEMBOLSO_Y_EQUIVALENTE_A_LA_FACTURA.xlsx
+++ b/public/templates/AUTORIZACION_DE_DESEMBOLSO_Y_EQUIVALENTE_A_LA_FACTURA.xlsx
@@ -5079,49 +5079,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>643417</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96F8D509-BDAB-38D0-2867-1891D34604FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect t="20324" b="8172"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2136937" y="9174480"/>
-          <a:ext cx="1292063" cy="327660"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
